--- a/Thesis_TSSP_NEWNEW_M1_Results_1_Scenarios.xlsx
+++ b/Thesis_TSSP_NEWNEW_M1_Results_1_Scenarios.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 14:24</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:27</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:33</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:05</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 13:54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:51</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.9460 sec</t>
+          <t>1.1710 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.0000 %</t>
+          <t>0.2188 %</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10.56</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="32">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.79</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.68</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="35">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25.68</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="39">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.95</v>
+        <v>34.23</v>
       </c>
     </row>
   </sheetData>
